--- a/artfynd/A 55135-2021 artfynd.xlsx
+++ b/artfynd/A 55135-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55135-2021 artfynd.xlsx
+++ b/artfynd/A 55135-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89224328</v>
+        <v>96376351</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1988</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kalkbarrskog N Försjön, Sm</t>
+          <t>Kalkbarrskog N om Försjön, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538360.7616108604</v>
+        <v>538306</v>
       </c>
       <c r="R2" t="n">
-        <v>6360966.959294096</v>
+        <v>6360974</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-09-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-09-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,7 +777,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -804,15 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96376320</v>
+        <v>96376231</v>
       </c>
       <c r="B3" t="n">
-        <v>88902</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,21 +799,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5734</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Druvfingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria botrytis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bourdot</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -855,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538292.8257168285</v>
+        <v>538325</v>
       </c>
       <c r="R3" t="n">
-        <v>6361013.212251102</v>
+        <v>6360968</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,19 +867,9 @@
           <t>2021-09-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson</t>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson, Stina Kullingsjö</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -932,15 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96376231</v>
+        <v>96376331</v>
       </c>
       <c r="B4" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,21 +912,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -983,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538325.1132223248</v>
+        <v>538293</v>
       </c>
       <c r="R4" t="n">
-        <v>6360967.702904672</v>
+        <v>6361013</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,19 +980,9 @@
           <t>2021-09-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,7 +1003,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson, Stina Kullingsjö</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1060,37 +1014,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96376331</v>
+        <v>96376166</v>
       </c>
       <c r="B5" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91424</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5420</v>
+        <v>5733</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1111,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538292.8257168285</v>
+        <v>538421</v>
       </c>
       <c r="R5" t="n">
-        <v>6361013.212251102</v>
+        <v>6360924</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,19 +1093,9 @@
           <t>2021-09-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,10 +1116,445 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson, Stina Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>88987032</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog N Försjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>538360</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6360929</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Järeda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-09-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-09-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Tobias Ivarsson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>115009492</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Försjöns kalkbarrskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>538348</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6360928</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Järeda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>89224328</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog N Försjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>538361</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6360967</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Järeda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-09-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-09-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>89224330</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog N Försjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>538281</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6360980</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Järeda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-09-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-09-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>

--- a/artfynd/A 55135-2021 artfynd.xlsx
+++ b/artfynd/A 55135-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96376351</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96376231</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96376331</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96376166</t>
         </is>
       </c>
     </row>
@@ -1229,6 +1254,11 @@
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88987032</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1331,6 +1361,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115009492</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1445,6 +1480,11 @@
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89224328</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1559,8 +1599,23 @@
           <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89224330</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>